--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260825.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260825.xlsx
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>84,899,363</t>
+          <t>156,567,694</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>156,567,694</t>
+          <t>84,899,363</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>441,126,781</t>
+          <t>23,609,273</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>23,609,273</t>
+          <t>441,126,781</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>25,493,288</t>
+          <t>22,584,009</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>22,584,009</t>
+          <t>25,493,288</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
